--- a/consolidated.xlsx
+++ b/consolidated.xlsx
@@ -440,20 +440,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="33" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="39" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -464,50 +463,45 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Aprobada</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Versión</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha de Publicación</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Últ. Fecha Publicación</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Últ. Commit GitHub</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Licencia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Aprobada</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Estado / Comentario</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Dependencias Directas</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Dependencias Transitivas</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Dependencias Rechazadas</t>
+          <t>URL</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Fecha de Publicación</t>
+          <t>Dependencias</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
@@ -516,456 +510,4160 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>numpy</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2.4.1</t>
+          <t>absl-py</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>2.4.0</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sin problemas detectados</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://pypi.org/project/absl-py</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://pypi.org/project/numpy</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Fundamental package for array computing in Python</t>
+          <t>Abseil Python Common Libraries, see https://github.com/abseil/abseil-py.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pandas</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>3.0.0</t>
+          <t>alembic</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>1.18.4</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Sin problemas detectados</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>numpy==2.4.1, python-dateutil==2.9.0.post0, tzdata==2025.3</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>six==1.17.0</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://pypi.org/project/alembic</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>mako</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://pypi.org/project/pandas</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Powerful data structures for data analysis, time series, and statistics</t>
+          <t>A database migration tool for SQLAlchemy.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pyodbc</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>5.3.0</t>
+          <t>annotated-doc</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>0.0.4</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Sin problemas detectados</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://pypi.org/project/annotated-doc</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://github.com/mkleehammer/pyodbc</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>DB API module for ODBC</t>
+          <t>Document parameters, class attributes, return types, and variables inline, with Annotated.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>python-dateutil</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2.9.0.post0</t>
+          <t>annotated-types</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Apache</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>0.7.0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sin problemas detectados</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>six==1.17.0</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://pypi.org/project/annotated-types</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://github.com/dateutil/dateutil</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Extensions to the standard Python datetime module</t>
+          <t>Reusable constraint types to use with typing.Annotated</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pywin32</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>311</t>
+          <t>anyio</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PSF</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>4.12.1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sin problemas detectados</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://pypi.org/project/anyio</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>idna</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://pypi.org/project/pywin32</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Python for Window Extensions</t>
+          <t>High-level concurrency and networking framework on top of asyncio or Trio</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>six</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1.17.0</t>
+          <t>blinker</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>1.9.0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Sin problemas detectados</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://pypi.org/project/blinker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://github.com/benjaminp/six</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Python 2 and 3 compatibility utilities</t>
+          <t>Fast, simple object-to-object and broadcast signaling</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tzdata</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2025.3</t>
+          <t>cachetools</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>5.5.2</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sin problemas detectados</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://github.com/tkem/cachetools/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://github.com/python/tzdata</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Provider of IANA time zone data</t>
+          <t>Extensible memoizing collections and decorators</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>unidecode</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1.4.0</t>
+          <t>cffi</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>2.0.0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/cffi</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>pycparser</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Foreign Function Interface for Python calling C code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>clarabel</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.11.1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/clarabel</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>cffi, pycparser</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Clarabel Conic Interior Point Solver for Rust / Python</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cloudpickle</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.1.2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>BSD</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://github.com/cloudpipe/cloudpickle</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Pickler class to extend the standard pickle.Pickler functionality</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>contourpy</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1.3.3</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>BSD 3-Clause</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/contourpy</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Python library for calculating contours of 2D quadrilateral grids</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cvxpy</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1.7.5</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Apache</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/cvxpy</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>clarabel, osqp, scs, cffi, pycparser, jinja2, markupsafe, setuptools</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>A domain-specific language for modeling convex optimization problems in Python.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cycler</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.12.1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>BSD</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/cycler</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Composable style cycles</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>docker</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>7.1.0</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Apache</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/docker</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>pywin32</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>A Python library for the Docker Engine API.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>entrypoints</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2022-02-02</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2022-02-02</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://github.com/takluyver/entrypoints</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Discover and load entry points from installed packages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>et-xmlfile</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2.0.0</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://foss.heptapod.net/openpyxl/et_xmlfile</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>An implementation of lxml.xmlfile for the standard library</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>fastapi</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.133.1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/fastapi</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>annotated-doc, pydantic, starlette, annotated-types, pydantic-core, anyio, idna</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>FastAPI framework, high performance, easy to learn, fast to code, ready for production</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>flask</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.1.3</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>BSD</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/flask</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>blinker, itsdangerous, werkzeug</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>A simple framework for building complex web applications.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>fonttools</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>4.61.1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>http://github.com/fonttools/fonttools</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Tools to manipulate font files</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>gitdb</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>4.0.12</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>BSD License</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://github.com/gitpython-developers/gitdb</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>smmap</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Git Object Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>gitpython</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3.1.46</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>BSD</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://github.com/gitpython-developers/GitPython</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>gitdb, smmap</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>GitPython is a Python library used to interact with Git repositories</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>graphene</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>3.4.3</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://github.com/graphql-python/graphene</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>graphql-relay, graphql-relay</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>GraphQL Framework for Python</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>graphql-relay</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3.2.0</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2022-04-16</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2022-04-16</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2023-02-27</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://github.com/graphql-python/graphql-relay-py</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Relay library for graphql-core</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>idna</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>BSD</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/idna</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Internationalized Domain Names in Applications (IDNA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>immutabledict</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>4.3.1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/immutabledict</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Immutable wrapper around dictionaries (a fork of frozendict)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>itsdangerous</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2.2.0</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2024-04-16</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2024-04-16</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>BSD License</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/itsdangerous</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Safely pass data to untrusted environments and back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>jinja2</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3.1.6</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>BSD License</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/jinja2</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>markupsafe</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>A very fast and expressive template engine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>joblib</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1.5.3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>BSD</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/joblib</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Lightweight pipelining with Python functions</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>kiwisolver</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1.4.9</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>BSD License</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/kiwisolver</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>A fast implementation of the Cassowary constraint solver</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>mako</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1.3.10</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.makotemplates.org/</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>A super-fast templating language that borrows the best ideas from the existing templating languages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>markdown</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>3.10.2</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>BSD</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/markdown</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Python implementation of John Gruber's Markdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>markupsafe</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>3.0.3</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>BSD</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/markupsafe</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Safely add untrusted strings to HTML/XML markup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>matplotlib</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>3.10.8</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/matplotlib</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>contourpy, cycler, fonttools, kiwisolver, pillow, pyparsing</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Python plotting package</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>matplotlib</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>3.9.0</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Python Software Foundation</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/matplotlib</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>contourpy, cycler, fonttools, kiwisolver, packaging, pillow, pyparsing, python-dateutil, six</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Python plotting package</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>mlflow</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2.13.0</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2024-05-20</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Apache</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/mlflow</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>alembic, cachetools, cloudpickle, docker, entrypoints, flask, gitpython, graphene, markdown, matplotlib, opentelemetry-sdk, pandas, protobuf, pyarrow, pyyaml, querystring-parser, scikit-learn, sqlparse, waitress, mako, pywin32, blinker, itsdangerous, werkzeug, gitdb, smmap, graphql-relay, contourpy, cycler, fonttools, kiwisolver, pillow, pyparsing, opentelemetry-semantic-conventions, tzdata, joblib, threadpoolctl, graphql-relay, protobuf, pyarrow, querystring-parser</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>MLflow is an open source platform for the complete machine learning lifecycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>numpy</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1.26.4</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2024-02-05</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://numpy.org</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Fundamental package for array computing in Python</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>numpy</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2.4.2</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/numpy</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Fundamental package for array computing in Python</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>openpyxl</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3.1.3</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://openpyxl.readthedocs.io</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>et-xmlfile</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>A Python library to read/write Excel 2010 xlsx/xlsm files</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>opentelemetry-sdk</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1.39.1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/opentelemetry-sdk</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>opentelemetry-semantic-conventions</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>OpenTelemetry Python SDK</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>opentelemetry-semantic-conventions</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0.60b1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/opentelemetry-semantic-conventions</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>OpenTelemetry Semantic Conventions</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>optbinning</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>0.19.0</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2024-01-15</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Apache</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://github.com/guillermo-navas-palencia/optbinning</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>matplotlib, ortools, ropwr, contourpy, cycler, fonttools, kiwisolver, packaging, pillow, pyparsing, absl-py, immutabledict, protobuf, typing-extensions, cvxpy, clarabel, cffi, pycparser, osqp, jinja2, markupsafe, setuptools, scs, protobuf</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>OptBinning: The Python Optimal Binning library</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ortools</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>9.14.6206</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://developers.google.com/optimization/</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>absl-py, immutabledict, protobuf, typing-extensions, protobuf</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Google OR-Tools python libraries and modules</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>osqp</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1.1.1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/osqp</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>jinja2, setuptools, markupsafe</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>OSQP: The Operator Splitting QP Solver</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>packaging</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>BSD</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/packaging</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Core utilities for Python packages</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>pandas</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2.2.2</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>BSD 3-Clause</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://pandas.pydata.org</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>numpy, python-dateutil, pytz, tzdata, six</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Powerful data structures for data analysis, time series, and statistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>pandas</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2.3.3</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/pandas</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>tzdata</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Powerful data structures for data analysis, time series, and statistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>pandas</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/pandas</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>tzdata</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Powerful data structures for data analysis, time series, and statistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>pillow</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>12.1.1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/pillow</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Python Imaging Library (fork)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>pip-chill</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1.0.3</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2023-04-15</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2023-04-15</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
           <t>GPL</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://github.com/rbanffy/pip-chill</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Like `pip freeze` but lists only the packages that are not dependencies of installed packages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>protobuf</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Licencia rechazada por política</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2025-04-24</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>https://pypi.org/project/unidecode</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>ASCII transliterations of Unicode text</t>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>4.25.8</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>3-Clause BSD License</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://developers.google.com/protocol-buffers/</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>protobuf</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>6.31.1</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>3-Clause BSD License</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://developers.google.com/protocol-buffers/</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>pyarrow</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>15.0.2</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Apache</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://arrow.apache.org/</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Python library for Apache Arrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>pycparser</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>BSD</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/pycparser</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>C parser in Python</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>pydantic</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2.12.5</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/pydantic</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>annotated-types, pydantic-core</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Data validation using Python type hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>pydantic-core</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2.41.5</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://github.com/pydantic/pydantic-core</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Core functionality for Pydantic validation and serialization</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>pyodbc</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>5.1.0</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2024-02-05</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://github.com/mkleehammer/pyodbc</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>DB API module for ODBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>pyparsing</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>3.3.2</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/pyparsing</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>pyparsing - Classes and methods to define and execute parsing grammars</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>pyprojroot</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>0.3.0</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2023-03-13</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2023-03-13</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/pyprojroot</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>typing-extensions</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Project-oriented workflow in Python</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>python-dateutil</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2.9.0.post0</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Apache</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://github.com/dateutil/dateutil</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>six</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Extensions to the standard Python datetime module</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>python-dotenv</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1.0.1</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2024-01-23</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>BSD</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://github.com/theskumar/python-dotenv</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Read key-value pairs from a .env file and set them as environment variables</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>pytz</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2025.2</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>http://pythonhosted.org/pytz</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>World timezone definitions, modern and historical</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>pywin32</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>PSF</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/pywin32</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Python for Window Extensions</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>pyyaml</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>6.0.3</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://pyyaml.org/</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>YAML parser and emitter for Python</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>querystring-parser</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1.2.4</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2020-10-21</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2020-10-21</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://github.com/bernii/querystring-parser</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>QueryString parser for Python/Django that correctly handles nested dictionaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ropwr</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1.2.0</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Apache</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://github.com/guillermo-navas-palencia/ropwr</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>cvxpy, clarabel, cffi, pycparser, osqp, jinja2, markupsafe, setuptools, scs</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>RoPWR: Robust Piecewise Regression</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>scikit-learn</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1.5.0</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>BSD</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://scikit-learn.org</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>joblib, scipy, threadpoolctl</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>A set of python modules for machine learning and data mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>scikit-learn</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1.8.0</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>BSD</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/scikit-learn</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>joblib, threadpoolctl</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>A set of python modules for machine learning and data mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>scipy</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1.17.1</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>BSD</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/scipy</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Fundamental algorithms for scientific computing in Python</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>scs</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>3.2.11</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/scs</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Splitting conic solver</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>seaborn</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>0.13.2</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2024-01-25</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2024-01-25</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>BSD License</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/seaborn</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>matplotlib, pandas, contourpy, cycler, fonttools, kiwisolver, packaging, pillow, pyparsing, tzdata</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Statistical data visualization</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>setuptools</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>82.0.0</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/setuptools</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Easily download, build, install, upgrade, and uninstall Python packages</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>six</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1.17.0</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://github.com/benjaminp/six</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Python 2 and 3 compatibility utilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>smmap</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>5.0.2</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>BSD</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://github.com/gitpython-developers/smmap</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>A pure Python implementation of a sliding window memory map manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>sqlparse</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>0.5.5</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>BSD License</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/sqlparse</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>A non-validating SQL parser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>starlette</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>0.52.1</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>BSD</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/starlette</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>anyio, idna</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>The little ASGI library that shines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>threadpoolctl</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>3.6.0</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>BSD</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://github.com/joblib/threadpoolctl</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>threadpoolctl</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>typing-extensions</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>4.15.0</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>PSF</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/typing-extensions</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Backported and Experimental Type Hints for Python 3.9+</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>tzdata</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2025.3</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://github.com/python/tzdata</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Provider of IANA time zone data</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>waitress</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>3.0.2</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>ZPL</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://github.com/Pylons/waitress</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Waitress WSGI server</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>werkzeug</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>3.1.6</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>BSD</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/werkzeug</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>The comprehensive WSGI web application library.</t>
         </is>
       </c>
     </row>
